--- a/outputs/analysis/budget_recommendation.xlsx
+++ b/outputs/analysis/budget_recommendation.xlsx
@@ -483,13 +483,13 @@
         <v>1186809.5</v>
       </c>
       <c r="C2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>89016</v>
@@ -498,7 +498,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.08</v>
+        <v>0.0750044552221734</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
